--- a/main/ig/FRSectionLaboratorySecondIntentionResultsLMCDAFHIR.xlsx
+++ b/main/ig/FRSectionLaboratorySecondIntentionResultsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRSectionLaboratorySecondIntentionResultsLMCDAFHIR.xlsx
+++ b/main/ig/FRSectionLaboratorySecondIntentionResultsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRSectionLaboratorySecondIntentionResultsLMCDAFHIR.xlsx
+++ b/main/ig/FRSectionLaboratorySecondIntentionResultsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRSectionLaboratorySecondIntentionResultsLMCDAFHIR.xlsx
+++ b/main/ig/FRSectionLaboratorySecondIntentionResultsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRSectionLaboratorySecondIntentionResultsLMCDAFHIR.xlsx
+++ b/main/ig/FRSectionLaboratorySecondIntentionResultsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRSectionLaboratorySecondIntentionResultsLMCDAFHIR.xlsx
+++ b/main/ig/FRSectionLaboratorySecondIntentionResultsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRSectionLaboratorySecondIntentionResultsLMCDAFHIR.xlsx
+++ b/main/ig/FRSectionLaboratorySecondIntentionResultsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRSectionLaboratorySecondIntentionResultsLMCDAFHIR.xlsx
+++ b/main/ig/FRSectionLaboratorySecondIntentionResultsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,13 +100,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-resultats-laboratoire-biologie-seconde-intention</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-resultats-laboratoire-biologie-seconde-intention</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-resultats-de-laboratoire-de-biologie-de-seconde-intention</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-resultats-de-laboratoire-de-biologie-de-seconde-intention</t>
   </si>
   <si>
     <t>FRLMResultatsLaboratoireBiologieSecondeIntention</t>
@@ -148,7 +148,7 @@
     <t>FRCDAResultatsDeLaboratoireDeBiologieDeSecondeIntention.entry:FRCDADocumentAttache</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-composition-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-composition-document|0.1.0</t>
   </si>
   <si>
     <t>FRCompositionDocument.section:sans-sous-sections</t>

--- a/main/ig/FRSectionLaboratorySecondIntentionResultsLMCDAFHIR.xlsx
+++ b/main/ig/FRSectionLaboratorySecondIntentionResultsLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="53">
   <si>
     <t>Property</t>
   </si>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:45:34+00:00</t>
+    <t>2026-08-31T15:12:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -106,7 +106,7 @@
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-resultats-de-laboratoire-de-biologie-de-seconde-intention</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-resultats-de-biologie-de-seconde-intention|0.1.0</t>
   </si>
   <si>
     <t>FRLMResultatsLaboratoireBiologieSecondeIntention</t>
@@ -115,58 +115,64 @@
     <t>equivalent</t>
   </si>
   <si>
+    <t>Section</t>
+  </si>
+  <si>
     <t>FRCDAResultatsDeLaboratoireDeBiologieDeSecondeIntention</t>
   </si>
   <si>
     <t>FRLMResultatsLaboratoireBiologieSecondeIntention.codeSection</t>
   </si>
   <si>
-    <t>FRCDAResultatsDeLaboratoireDeBiologieDeSecondeIntention.code</t>
+    <t>Section.code</t>
   </si>
   <si>
     <t>FRLMResultatsLaboratoireBiologieSecondeIntention.titreSection</t>
   </si>
   <si>
-    <t>FRCDAResultatsDeLaboratoireDeBiologieDeSecondeIntention.title</t>
+    <t>Section.title</t>
   </si>
   <si>
     <t>FRLMResultatsLaboratoireBiologieSecondeIntention.blocNarratif</t>
   </si>
   <si>
-    <t>FRCDAResultatsDeLaboratoireDeBiologieDeSecondeIntention.text</t>
+    <t>Section.text</t>
   </si>
   <si>
     <t>FRLMResultatsLaboratoireBiologieSecondeIntention.entree.observation:FRLMObservation</t>
   </si>
   <si>
-    <t>FRCDAResultatsDeLaboratoireDeBiologieDeSecondeIntention.entry:FRCDASimpleObservation</t>
+    <t>Section.entry:FRCDASimpleObservation</t>
   </si>
   <si>
     <t>FRLMResultatsLaboratoireBiologieSecondeIntention.entree.documentAttache:FRLMDocumentAttache</t>
   </si>
   <si>
-    <t>FRCDAResultatsDeLaboratoireDeBiologieDeSecondeIntention.entry:FRCDADocumentAttache</t>
+    <t>Section.entry:FRCDADocumentAttache</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-composition-document|0.1.0</t>
   </si>
   <si>
-    <t>FRCompositionDocument.section:sans-sous-sections</t>
-  </si>
-  <si>
-    <t>FRCompositionDocument.section:sans-sous-sections.code</t>
-  </si>
-  <si>
-    <t>FRCompositionDocument.section:sans-sous-sections.title</t>
-  </si>
-  <si>
-    <t>FRCompositionDocument.section:sans-sous-sections.text</t>
-  </si>
-  <si>
-    <t>FRCompositionDocument.section:sans-sous-sections.entry:FRObservationLaboratoryReportResultsDocument</t>
-  </si>
-  <si>
-    <t>FRCompositionDocument.section:sans-sous-sections.entry:FRDocumentReferenceDocument</t>
+    <t>Composition.section:sans-sous-sections</t>
+  </si>
+  <si>
+    <t>FRCompositionDocument.section:sans</t>
+  </si>
+  <si>
+    <t>Composition.section:sans-sous-sections.code</t>
+  </si>
+  <si>
+    <t>Composition.section:sans-sous-sections.title</t>
+  </si>
+  <si>
+    <t>Composition.section:sans-sous-sections.text</t>
+  </si>
+  <si>
+    <t>Composition.section:sans-sous-sections.entry:FRObservationLaboratoryReportResultsDocument</t>
+  </si>
+  <si>
+    <t>Composition.section:sans-sous-sections.entry:FRDocumentReferenceDocument</t>
   </si>
 </sst>
 </file>
@@ -466,70 +472,72 @@
       <c r="D3" t="s" s="2">
         <v>33</v>
       </c>
-      <c r="E3" s="2"/>
+      <c r="E3" t="s" s="2">
+        <v>34</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E8" s="2"/>
     </row>
@@ -571,7 +579,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>29</v>
@@ -586,72 +594,74 @@
         <v>32</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="E3" s="2"/>
+        <v>46</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>47</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E8" s="2"/>
     </row>

--- a/main/ig/FRSectionLaboratorySecondIntentionResultsLMCDAFHIR.xlsx
+++ b/main/ig/FRSectionLaboratorySecondIntentionResultsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:12:23+00:00</t>
+    <t>2026-09-04T14:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
